--- a/artfynd/A 34096-2022 artfynd.xlsx
+++ b/artfynd/A 34096-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34096-2022 artfynd.xlsx
+++ b/artfynd/A 34096-2022 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>121140851</v>
       </c>
       <c r="B4" t="n">
-        <v>89348</v>
+        <v>89358</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 34096-2022 artfynd.xlsx
+++ b/artfynd/A 34096-2022 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>121140851</v>
       </c>
       <c r="B4" t="n">
-        <v>89358</v>
+        <v>89365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 34096-2022 artfynd.xlsx
+++ b/artfynd/A 34096-2022 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>121140851</v>
       </c>
       <c r="B4" t="n">
-        <v>89365</v>
+        <v>89366</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 34096-2022 artfynd.xlsx
+++ b/artfynd/A 34096-2022 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>121140851</v>
       </c>
       <c r="B4" t="n">
-        <v>89366</v>
+        <v>89369</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 34096-2022 artfynd.xlsx
+++ b/artfynd/A 34096-2022 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>131733383</v>
       </c>
       <c r="B5" t="n">
-        <v>92547</v>
+        <v>92550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34096-2022 artfynd.xlsx
+++ b/artfynd/A 34096-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68622706</v>
+        <v>121140851</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1596</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mjöldammen, Ög</t>
+          <t>Lotorps naturreservat, Lotorps naturreservat, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546432.303739182</v>
+        <v>546526</v>
       </c>
       <c r="R2" t="n">
-        <v>6509309.195388668</v>
+        <v>6509529</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-11-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-11-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,34 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hilda-Linn Berglund</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hilda-Linn Berglund</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68622864</v>
+        <v>131732799</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,47 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mjöldammen, Ög</t>
+          <t>Mjöldammen Nordväst, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546498.5877618975</v>
+        <v>546413</v>
       </c>
       <c r="R3" t="n">
-        <v>6509379.064724375</v>
+        <v>6509313</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-11-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-11-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,72 +851,72 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hilda-Linn Berglund</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hilda-Linn Berglund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121140851</v>
+        <v>68622706</v>
       </c>
       <c r="B4" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1596</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lotorps naturreservat, Lotorps naturreservat, Ög</t>
+          <t>Mjöldammen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546526</v>
+        <v>546432</v>
       </c>
       <c r="R4" t="n">
-        <v>6509529</v>
+        <v>6509309</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,12 +940,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2017-11-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2017-11-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,66 +954,77 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hilda-Linn Berglund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hilda-Linn Berglund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131733383</v>
+        <v>68622864</v>
       </c>
       <c r="B5" t="n">
-        <v>92550</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mjöldammen Nordväst, Ög</t>
+          <t>Mjöldammen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546443</v>
+        <v>546499</v>
       </c>
       <c r="R5" t="n">
-        <v>6509284</v>
+        <v>6509379</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,12 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2017-11-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2017-11-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,21 +1062,220 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Hilda-Linn Berglund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hilda-Linn Berglund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131737865</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93309</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mjöldammen Nordväst, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>546417</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6509289</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131733383</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92651</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mjöldammen Nordväst, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>546443</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6509284</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 34096-2022 artfynd.xlsx
+++ b/artfynd/A 34096-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121140851</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732799</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -970,6 +985,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68622706</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68622864</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737865</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,8 +1310,21 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733383</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>